--- a/artfynd/A 37889-2022 artfynd.xlsx
+++ b/artfynd/A 37889-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37889-2022 artfynd.xlsx
+++ b/artfynd/A 37889-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2321,6 +2321,875 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114928961</v>
+      </c>
+      <c r="B16" t="n">
+        <v>77842</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6436</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gulpudrad spiklav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Calicium adspersum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tuna 199, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>570144</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6378192</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114929757</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8405</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tuna 199, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>570251</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6378094</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>114929930</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79048</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tuna 199, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>570263</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6378085</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>114929285</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90263</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tuna 199, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>570144</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6378192</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>114929887</v>
+      </c>
+      <c r="B20" t="n">
+        <v>77842</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6436</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gulpudrad spiklav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Calicium adspersum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tuna 199, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>570263</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6378085</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>114929371</v>
+      </c>
+      <c r="B21" t="n">
+        <v>90263</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tuna 199, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>570157</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6378156</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>114929116</v>
+      </c>
+      <c r="B22" t="n">
+        <v>90806</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1143</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blekticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Haploporus tuberculosus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tuna 199, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>570144</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6378192</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>114929618</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90263</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tuna 199, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>570194</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6378131</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37889-2022 artfynd.xlsx
+++ b/artfynd/A 37889-2022 artfynd.xlsx
@@ -3307,7 +3307,7 @@
         <v>115756805</v>
       </c>
       <c r="B25" t="n">
-        <v>57271</v>
+        <v>57484</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 37889-2022 artfynd.xlsx
+++ b/artfynd/A 37889-2022 artfynd.xlsx
@@ -3307,7 +3307,7 @@
         <v>115756805</v>
       </c>
       <c r="B25" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 37889-2022 artfynd.xlsx
+++ b/artfynd/A 37889-2022 artfynd.xlsx
@@ -3307,7 +3307,7 @@
         <v>115756805</v>
       </c>
       <c r="B25" t="n">
-        <v>57487</v>
+        <v>57493</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 37889-2022 artfynd.xlsx
+++ b/artfynd/A 37889-2022 artfynd.xlsx
@@ -3307,7 +3307,7 @@
         <v>115756805</v>
       </c>
       <c r="B25" t="n">
-        <v>57493</v>
+        <v>57496</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 37889-2022 artfynd.xlsx
+++ b/artfynd/A 37889-2022 artfynd.xlsx
@@ -3307,7 +3307,7 @@
         <v>115756805</v>
       </c>
       <c r="B25" t="n">
-        <v>57496</v>
+        <v>57497</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 37889-2022 artfynd.xlsx
+++ b/artfynd/A 37889-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109610157</v>
+        <v>109610046</v>
       </c>
       <c r="B2" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1114</v>
+        <v>226</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelekslav</t>
+          <t>Skuggorangelav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lecanographa amylacea</t>
+          <t>Caloplaca lucifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
+          <t>G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570241.614467465</v>
+        <v>570259</v>
       </c>
       <c r="R2" t="n">
-        <v>6378090.47159162</v>
+        <v>6378082</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109610117</v>
+        <v>109610047</v>
       </c>
       <c r="B3" t="n">
-        <v>76907</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6436</v>
+        <v>226</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Skuggorangelav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Caloplaca lucifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570268.7609329757</v>
+        <v>570269</v>
       </c>
       <c r="R3" t="n">
-        <v>6378075.908946216</v>
+        <v>6378076</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,19 +845,9 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109610215</v>
+        <v>109610048</v>
       </c>
       <c r="B4" t="n">
-        <v>89953</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80703</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1143</v>
+        <v>226</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blekticka</t>
+          <t>Skuggorangelav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus tuberculosus</t>
+          <t>Caloplaca lucifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
+          <t>G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570148.5046844906</v>
+        <v>570150</v>
       </c>
       <c r="R4" t="n">
-        <v>6378187.106171146</v>
+        <v>6378188</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -982,21 +947,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1008,7 +963,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>ekved</t>
+          <t>ek</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1026,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109610118</v>
+        <v>109610087</v>
       </c>
       <c r="B5" t="n">
-        <v>76907</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6436</v>
+        <v>306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570150.1363719002</v>
+        <v>570150</v>
       </c>
       <c r="R5" t="n">
-        <v>6378186.060656526</v>
+        <v>6378188</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,19 +1049,9 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109610087</v>
+        <v>109610202</v>
       </c>
       <c r="B6" t="n">
-        <v>73680</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570150.0993197775</v>
+        <v>570260</v>
       </c>
       <c r="R6" t="n">
-        <v>6378188.207370922</v>
+        <v>6378082</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1216,19 +1151,9 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,59 +1185,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109610085</v>
+        <v>109610204</v>
       </c>
       <c r="B7" t="n">
-        <v>9491</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101479</v>
+        <v>311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Läderbagge</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Osmoderma eremita</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570254.7148784021</v>
+        <v>570269</v>
       </c>
       <c r="R7" t="n">
-        <v>6378079.424110251</v>
+        <v>6378076</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1342,28 +1253,17 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1380,22 +1280,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Mikael Hagström, Pontus Axén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109610046</v>
+        <v>115744184</v>
       </c>
       <c r="B8" t="n">
-        <v>78840</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,37 +1298,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>226</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skuggorangelav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Caloplaca lucifuga</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>G.Thor</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Väderum, Sm</t>
+          <t>Bron, Bron, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570258.4233585296</v>
+        <v>570140</v>
       </c>
       <c r="R8" t="n">
-        <v>6378082.709331136</v>
+        <v>6378189</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1457,22 +1352,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,58 +1378,48 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>ek</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109610202</v>
+        <v>109610157</v>
       </c>
       <c r="B9" t="n">
-        <v>73690</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>311</v>
+        <v>1114</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1544,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570260.574295981</v>
+        <v>570241</v>
       </c>
       <c r="R9" t="n">
-        <v>6378082.746512689</v>
+        <v>6378090</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1577,19 +1462,9 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,44 +1489,39 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109610204</v>
+        <v>109610215</v>
       </c>
       <c r="B10" t="n">
-        <v>73690</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92510</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>311</v>
+        <v>1143</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Blekticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Haploporus tuberculosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1661,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570268.7609329757</v>
+        <v>570148</v>
       </c>
       <c r="R10" t="n">
-        <v>6378075.908946216</v>
+        <v>6378187</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1694,21 +1564,11 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-05-22</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1720,7 +1580,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>ek</t>
+          <t>ekved</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1738,15 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109610111</v>
+        <v>114929116</v>
       </c>
       <c r="B11" t="n">
-        <v>78008</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92510</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,34 +1609,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1348</v>
+        <v>1143</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hjälmbrosklav</t>
+          <t>Blekticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramalina baltica</t>
+          <t>Haploporus tuberculosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Lettau</t>
+          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väderum, Sm</t>
+          <t>Tuna 199, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570268.7609329757</v>
+        <v>570145</v>
       </c>
       <c r="R11" t="n">
-        <v>6378075.908946216</v>
+        <v>6378192</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1808,22 +1664,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,36 +1680,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>ek</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109610047</v>
+        <v>115756997</v>
       </c>
       <c r="B12" t="n">
-        <v>78840</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92510</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,37 +1707,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>226</v>
+        <v>1143</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skuggorangelav</t>
+          <t>Blekticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Caloplaca lucifuga</t>
+          <t>Haploporus tuberculosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>G.Thor</t>
+          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Väderum, Sm</t>
+          <t>A 37889, Väderum, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>570268.7609329757</v>
+        <v>570147</v>
       </c>
       <c r="R12" t="n">
-        <v>6378075.908946216</v>
+        <v>6378203</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1925,22 +1768,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På nedfallna grenar under stor ek</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,38 +1787,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>ek</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109610059</v>
+        <v>109610111</v>
       </c>
       <c r="B13" t="n">
-        <v>73615</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79847</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1988,21 +1817,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1460</v>
+        <v>1348</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Hjälmbrosklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Ramalina baltica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>Lettau</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2012,10 +1841,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570149.0887193923</v>
+        <v>570269</v>
       </c>
       <c r="R13" t="n">
-        <v>6378184.432058096</v>
+        <v>6378076</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2045,19 +1874,9 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,44 +1901,39 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109610116</v>
+        <v>109610059</v>
       </c>
       <c r="B14" t="n">
-        <v>76907</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6436</v>
+        <v>1460</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2129,10 +1943,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570264.3941046026</v>
+        <v>570149</v>
       </c>
       <c r="R14" t="n">
-        <v>6378079.591427315</v>
+        <v>6378184</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2162,19 +1976,9 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2206,15 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109610048</v>
+        <v>114929285</v>
       </c>
       <c r="B15" t="n">
-        <v>78840</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,34 +2021,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>226</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skuggorangelav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Caloplaca lucifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>G.Thor</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Väderum, Sm</t>
+          <t>Tuna 199, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570150.0993197775</v>
+        <v>570145</v>
       </c>
       <c r="R15" t="n">
-        <v>6378188.207370922</v>
+        <v>6378192</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2276,22 +2076,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2302,21 +2092,16 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>ek</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mikael Hagström, Pontus Axén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2326,12 +2111,7 @@
         <v>114929371</v>
       </c>
       <c r="B16" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2426,15 +2206,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114929116</v>
+        <v>114929618</v>
       </c>
       <c r="B17" t="n">
-        <v>90898</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,21 +2217,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1143</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Haploporus tuberculosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2467,10 +2242,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570145</v>
+        <v>570194</v>
       </c>
       <c r="R17" t="n">
-        <v>6378192</v>
+        <v>6378130</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2500,9 +2275,19 @@
           <t>2024-02-29</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2529,51 +2314,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>114929285</v>
+        <v>109610116</v>
       </c>
       <c r="B18" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78728</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>6436</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tuna 199, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570145</v>
+        <v>570265</v>
       </c>
       <c r="R18" t="n">
-        <v>6378192</v>
+        <v>6378080</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2600,12 +2379,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2616,31 +2395,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>ek</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114928961</v>
+        <v>109610117</v>
       </c>
       <c r="B19" t="n">
-        <v>77893</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78728</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2666,17 +2445,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tuna 199, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570145</v>
+        <v>570269</v>
       </c>
       <c r="R19" t="n">
-        <v>6378192</v>
+        <v>6378076</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2703,12 +2481,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2719,67 +2497,66 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>ek</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>114929930</v>
+        <v>109610118</v>
       </c>
       <c r="B20" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78728</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6436</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tuna 199, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570262</v>
+        <v>570150</v>
       </c>
       <c r="R20" t="n">
-        <v>6378086</v>
+        <v>6378186</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2806,22 +2583,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2832,67 +2599,66 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>ek</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114929618</v>
+        <v>109610119</v>
       </c>
       <c r="B21" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78728</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>6436</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tuna 199, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570194</v>
+        <v>570121</v>
       </c>
       <c r="R21" t="n">
-        <v>6378130</v>
+        <v>6378136</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2919,22 +2685,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:27</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:27</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2945,31 +2701,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>ek</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Pontus Axén, Mikael Hagström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>114929887</v>
+        <v>114928961</v>
       </c>
       <c r="B22" t="n">
-        <v>77893</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78728</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3002,10 +2758,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570262</v>
+        <v>570145</v>
       </c>
       <c r="R22" t="n">
-        <v>6378086</v>
+        <v>6378192</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3035,19 +2791,9 @@
           <t>2024-02-29</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,15 +2820,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>114929757</v>
+        <v>114929803</v>
       </c>
       <c r="B23" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78728</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3090,21 +2831,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6436</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3115,10 +2856,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>570252</v>
+        <v>570247</v>
       </c>
       <c r="R23" t="n">
-        <v>6378094</v>
+        <v>6378106</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3161,11 +2902,6 @@
       <c r="AB23" t="inlineStr">
         <is>
           <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3192,53 +2928,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115744184</v>
+        <v>114929887</v>
       </c>
       <c r="B24" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78728</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6436</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bron (Bron), Sm</t>
+          <t>Tuna 199, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>570140</v>
+        <v>570262</v>
       </c>
       <c r="R24" t="n">
-        <v>6378189</v>
+        <v>6378086</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3262,22 +2994,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3292,77 +3024,63 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115756805</v>
+        <v>115756864</v>
       </c>
       <c r="B25" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78728</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100048</v>
+        <v>6436</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 37889, Väderum, Sm</t>
+          <t>A 37889,  Väderum, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>570158</v>
+        <v>570270</v>
       </c>
       <c r="R25" t="n">
-        <v>6378161</v>
+        <v>6378094</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3394,12 +3112,18 @@
           <t>2024-04-07</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På gammal ek</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3418,50 +3142,41 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115756997</v>
+        <v>116063003</v>
       </c>
       <c r="B26" t="n">
-        <v>90898</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78728</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1143</v>
+        <v>6436</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blekticka</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Haploporus tuberculosus</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 37889, Väderum, Sm</t>
+          <t>Väderum, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
@@ -3495,17 +3210,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På nedfallna grenar under stor ek</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3521,62 +3231,58 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115738010</v>
+        <v>114929930</v>
       </c>
       <c r="B27" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tuna 199, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>570145</v>
+        <v>570262</v>
       </c>
       <c r="R27" t="n">
-        <v>6378192</v>
+        <v>6378086</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3603,12 +3309,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3635,15 +3351,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115756751</v>
+        <v>115756805</v>
       </c>
       <c r="B28" t="n">
-        <v>57412</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3651,16 +3362,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3687,10 +3398,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>570197</v>
+        <v>570158</v>
       </c>
       <c r="R28" t="n">
-        <v>6378111</v>
+        <v>6378161</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3749,42 +3460,43 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>116063003</v>
+        <v>109610085</v>
       </c>
       <c r="B29" t="n">
-        <v>77893</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9596</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6436</v>
+        <v>101479</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Osmoderma eremita</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3792,13 +3504,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>570147</v>
+        <v>570254</v>
       </c>
       <c r="R29" t="n">
-        <v>6378203</v>
+        <v>6378080</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3822,12 +3534,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3840,18 +3552,578 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>ek</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>115029964</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Väderum, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>570228</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6378156</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>115756751</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>A 37889, Väderum, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>570197</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6378111</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-04-07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-04-07</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>114929757</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Tuna 199, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>570252</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6378094</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>115029962</v>
+      </c>
+      <c r="B33" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Väderum, smedserum, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>570228</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6378156</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>115738010</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Tuna 199, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>570145</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6378192</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-04-07</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-04-07</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37889-2022 artfynd.xlsx
+++ b/artfynd/A 37889-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610046</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610047</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610048</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610087</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610202</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610204</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115744184</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610157</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1595,6 +1640,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610215</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1693,6 +1743,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114929116</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1803,6 +1858,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115756997</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1905,6 +1965,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610111</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2007,6 +2072,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610059</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2105,6 +2175,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114929285</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2203,6 +2278,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114929371</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2311,6 +2391,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114929618</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2413,6 +2498,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610116</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2515,6 +2605,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610117</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2617,6 +2712,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610118</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2719,6 +2819,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610119</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2817,6 +2922,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114928961</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2925,6 +3035,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114929803</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3033,6 +3148,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114929887</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3139,6 +3259,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115756864</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3240,6 +3365,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116063003</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3348,6 +3478,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114929930</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3457,6 +3592,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115756805</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3569,6 +3709,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109610085</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3688,6 +3833,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115029964</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3797,6 +3947,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115756751</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3910,6 +4065,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114929757</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4027,6 +4187,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115029962</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4124,8 +4289,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115738010</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>